--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Chara.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Chara.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3765" uniqueCount="2509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3770" uniqueCount="2512">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -6838,6 +6838,12 @@
     <t xml:space="preserve">さまよう絵画</t>
   </si>
   <si>
+    <t xml:space="preserve">paint_living2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.355</t>
+  </si>
+  <si>
     <t xml:space="preserve">merchant_exotic</t>
   </si>
   <si>
@@ -6874,10 +6880,13 @@
     <t xml:space="preserve">beholder</t>
   </si>
   <si>
-    <t xml:space="preserve">비홀더</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ビホルダー</t>
+    <t xml:space="preserve">U-388 명칭 말소 개체</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naming Failure U-388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U-388 名称抹消個体</t>
   </si>
   <si>
     <t xml:space="preserve">evileye</t>
@@ -7778,7 +7787,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L604"/>
+  <dimension ref="A1:L605"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="1" style="0" width="16.15"/>
@@ -19196,202 +19205,202 @@
         <v>2271</v>
       </c>
       <c r="B556" s="0" t="s">
-        <v>565</v>
+        <v>2272</v>
       </c>
       <c r="D556" s="0" t="s">
-        <v>14</v>
+        <v>2268</v>
       </c>
       <c r="E556" s="0" t="s">
-        <v>14</v>
+        <v>2269</v>
       </c>
       <c r="F556" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J556" s="0" t="s">
-        <v>2272</v>
-      </c>
-      <c r="K556" s="0" t="s">
-        <v>2273</v>
-      </c>
-      <c r="L556" s="0" t="s">
-        <v>2274</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="557" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A557" s="0" t="s">
+        <v>2273</v>
+      </c>
+      <c r="B557" s="0" t="s">
+        <v>565</v>
+      </c>
+      <c r="D557" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="E557" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F557" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="J557" s="0" t="s">
+        <v>2274</v>
+      </c>
+      <c r="K557" s="0" t="s">
         <v>2275</v>
       </c>
-      <c r="B557" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D557" s="0" t="s">
+      <c r="L557" s="0" t="s">
         <v>2276</v>
-      </c>
-      <c r="E557" s="0" t="s">
-        <v>2275</v>
-      </c>
-      <c r="F557" s="0" t="s">
-        <v>2277</v>
       </c>
     </row>
     <row r="558" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A558" s="0" t="s">
+        <v>2277</v>
+      </c>
+      <c r="B558" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D558" s="0" t="s">
         <v>2278</v>
       </c>
-      <c r="B558" s="0" t="s">
-        <v>1250</v>
-      </c>
-      <c r="D558" s="0" t="s">
+      <c r="E558" s="0" t="s">
+        <v>2277</v>
+      </c>
+      <c r="F558" s="0" t="s">
         <v>2279</v>
-      </c>
-      <c r="E558" s="0" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F558" s="0" t="s">
-        <v>2281</v>
       </c>
     </row>
     <row r="559" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A559" s="0" t="s">
-        <v>2282</v>
+        <v>2280</v>
       </c>
       <c r="B559" s="0" t="s">
-        <v>728</v>
+        <v>1250</v>
       </c>
       <c r="D559" s="0" t="s">
-        <v>2283</v>
+        <v>2281</v>
       </c>
       <c r="E559" s="0" t="s">
         <v>2282</v>
       </c>
       <c r="F559" s="0" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="560" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A560" s="0" t="s">
+        <v>2284</v>
+      </c>
+      <c r="B560" s="0" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D560" s="0" t="s">
         <v>2285</v>
       </c>
-      <c r="B560" s="0" t="s">
-        <v>728</v>
-      </c>
-      <c r="D560" s="0" t="s">
+      <c r="E560" s="0" t="s">
         <v>2286</v>
       </c>
-      <c r="E560" s="0" t="s">
+      <c r="F560" s="0" t="s">
         <v>2287</v>
-      </c>
-      <c r="F560" s="0" t="s">
-        <v>2288</v>
       </c>
     </row>
     <row r="561" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A561" s="0" t="s">
+        <v>2288</v>
+      </c>
+      <c r="B561" s="0" t="s">
+        <v>728</v>
+      </c>
+      <c r="D561" s="0" t="s">
         <v>2289</v>
       </c>
-      <c r="B561" s="0" t="s">
-        <v>202</v>
-      </c>
-      <c r="D561" s="0" t="s">
-        <v>14</v>
-      </c>
       <c r="E561" s="0" t="s">
-        <v>14</v>
+        <v>2290</v>
       </c>
       <c r="F561" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J561" s="0" t="s">
-        <v>2290</v>
-      </c>
-      <c r="K561" s="0" t="s">
         <v>2291</v>
-      </c>
-      <c r="L561" s="0" t="s">
-        <v>2292</v>
       </c>
     </row>
     <row r="562" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A562" s="0" t="s">
+        <v>2292</v>
+      </c>
+      <c r="B562" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="D562" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="E562" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F562" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="J562" s="0" t="s">
         <v>2293</v>
       </c>
-      <c r="B562" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D562" s="0" t="s">
+      <c r="K562" s="0" t="s">
         <v>2294</v>
       </c>
-      <c r="E562" s="0" t="s">
+      <c r="L562" s="0" t="s">
         <v>2295</v>
-      </c>
-      <c r="F562" s="0" t="s">
-        <v>2296</v>
-      </c>
-      <c r="J562" s="0" t="s">
-        <v>2297</v>
-      </c>
-      <c r="K562" s="0" t="s">
-        <v>2298</v>
-      </c>
-      <c r="L562" s="0" t="s">
-        <v>2299</v>
       </c>
     </row>
     <row r="563" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A563" s="0" t="s">
-        <v>2300</v>
+        <v>2296</v>
       </c>
       <c r="B563" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D563" s="0" t="s">
+        <v>2297</v>
+      </c>
+      <c r="E563" s="0" t="s">
+        <v>2298</v>
+      </c>
+      <c r="F563" s="0" t="s">
+        <v>2299</v>
+      </c>
+      <c r="J563" s="0" t="s">
+        <v>2300</v>
+      </c>
+      <c r="K563" s="0" t="s">
         <v>2301</v>
       </c>
-      <c r="E563" s="0" t="s">
+      <c r="L563" s="0" t="s">
         <v>2302</v>
-      </c>
-      <c r="F563" s="0" t="s">
-        <v>2303</v>
-      </c>
-      <c r="J563" s="0" t="s">
-        <v>2304</v>
-      </c>
-      <c r="K563" s="0" t="s">
-        <v>2305</v>
-      </c>
-      <c r="L563" s="0" t="s">
-        <v>2306</v>
       </c>
     </row>
     <row r="564" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A564" s="0" t="s">
+        <v>2303</v>
+      </c>
+      <c r="B564" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D564" s="0" t="s">
+        <v>2304</v>
+      </c>
+      <c r="E564" s="0" t="s">
+        <v>2305</v>
+      </c>
+      <c r="F564" s="0" t="s">
+        <v>2306</v>
+      </c>
+      <c r="J564" s="0" t="s">
         <v>2307</v>
       </c>
-      <c r="B564" s="0" t="s">
+      <c r="K564" s="0" t="s">
         <v>2308</v>
       </c>
-      <c r="D564" s="0" t="s">
+      <c r="L564" s="0" t="s">
         <v>2309</v>
-      </c>
-      <c r="E564" s="0" t="s">
-        <v>2310</v>
-      </c>
-      <c r="F564" s="0" t="s">
-        <v>2311</v>
       </c>
     </row>
     <row r="565" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A565" s="0" t="s">
+        <v>2310</v>
+      </c>
+      <c r="B565" s="0" t="s">
+        <v>2311</v>
+      </c>
+      <c r="D565" s="0" t="s">
         <v>2312</v>
       </c>
-      <c r="B565" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D565" s="0" t="s">
+      <c r="E565" s="0" t="s">
         <v>2313</v>
-      </c>
-      <c r="E565" s="0" t="s">
-        <v>2312</v>
       </c>
       <c r="F565" s="0" t="s">
         <v>2314</v>
@@ -19419,7 +19428,7 @@
         <v>2318</v>
       </c>
       <c r="B567" s="0" t="s">
-        <v>595</v>
+        <v>13</v>
       </c>
       <c r="D567" s="0" t="s">
         <v>2319</v>
@@ -19436,24 +19445,15 @@
         <v>2321</v>
       </c>
       <c r="B568" s="0" t="s">
-        <v>13</v>
+        <v>595</v>
       </c>
       <c r="D568" s="0" t="s">
-        <v>14</v>
+        <v>2322</v>
       </c>
       <c r="E568" s="0" t="s">
-        <v>14</v>
+        <v>2321</v>
       </c>
       <c r="F568" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J568" s="0" t="s">
-        <v>2322</v>
-      </c>
-      <c r="K568" s="0" t="s">
-        <v>2321</v>
-      </c>
-      <c r="L568" s="0" t="s">
         <v>2323</v>
       </c>
     </row>
@@ -19477,15 +19477,15 @@
         <v>2325</v>
       </c>
       <c r="K569" s="0" t="s">
+        <v>2324</v>
+      </c>
+      <c r="L569" s="0" t="s">
         <v>2326</v>
-      </c>
-      <c r="L569" s="0" t="s">
-        <v>2327</v>
       </c>
     </row>
     <row r="570" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A570" s="0" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="B570" s="0" t="s">
         <v>13</v>
@@ -19500,21 +19500,21 @@
         <v>14</v>
       </c>
       <c r="J570" s="0" t="s">
-        <v>2322</v>
+        <v>2328</v>
       </c>
       <c r="K570" s="0" t="s">
-        <v>2321</v>
+        <v>2329</v>
       </c>
       <c r="L570" s="0" t="s">
-        <v>2323</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="571" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A571" s="0" t="s">
-        <v>2329</v>
+        <v>2331</v>
       </c>
       <c r="B571" s="0" t="s">
-        <v>990</v>
+        <v>13</v>
       </c>
       <c r="D571" s="0" t="s">
         <v>14</v>
@@ -19526,219 +19526,228 @@
         <v>14</v>
       </c>
       <c r="J571" s="0" t="s">
-        <v>2322</v>
+        <v>2325</v>
       </c>
       <c r="K571" s="0" t="s">
-        <v>2321</v>
+        <v>2324</v>
       </c>
       <c r="L571" s="0" t="s">
-        <v>2323</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="572" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A572" s="0" t="s">
-        <v>2330</v>
+        <v>2332</v>
       </c>
       <c r="B572" s="0" t="s">
-        <v>13</v>
+        <v>990</v>
       </c>
       <c r="D572" s="0" t="s">
-        <v>2331</v>
+        <v>14</v>
       </c>
       <c r="E572" s="0" t="s">
-        <v>2332</v>
+        <v>14</v>
       </c>
       <c r="F572" s="0" t="s">
-        <v>2333</v>
+        <v>14</v>
       </c>
       <c r="J572" s="0" t="s">
-        <v>2334</v>
+        <v>2325</v>
       </c>
       <c r="K572" s="0" t="s">
-        <v>2335</v>
+        <v>2324</v>
       </c>
       <c r="L572" s="0" t="s">
-        <v>2336</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="573" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A573" s="0" t="s">
-        <v>2337</v>
+        <v>2333</v>
       </c>
       <c r="B573" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D573" s="0" t="s">
+        <v>2334</v>
+      </c>
+      <c r="E573" s="0" t="s">
+        <v>2335</v>
+      </c>
+      <c r="F573" s="0" t="s">
+        <v>2336</v>
+      </c>
+      <c r="J573" s="0" t="s">
+        <v>2337</v>
+      </c>
+      <c r="K573" s="0" t="s">
         <v>2338</v>
       </c>
-      <c r="E573" s="0" t="s">
+      <c r="L573" s="0" t="s">
         <v>2339</v>
-      </c>
-      <c r="F573" s="0" t="s">
-        <v>2340</v>
-      </c>
-      <c r="J573" s="0" t="s">
-        <v>2341</v>
-      </c>
-      <c r="K573" s="0" t="s">
-        <v>2342</v>
-      </c>
-      <c r="L573" s="0" t="s">
-        <v>2343</v>
       </c>
     </row>
     <row r="574" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A574" s="0" t="s">
-        <v>2344</v>
+        <v>2340</v>
       </c>
       <c r="B574" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D574" s="0" t="s">
+        <v>2341</v>
+      </c>
+      <c r="E574" s="0" t="s">
+        <v>2342</v>
+      </c>
+      <c r="F574" s="0" t="s">
+        <v>2343</v>
+      </c>
+      <c r="J574" s="0" t="s">
+        <v>2344</v>
+      </c>
+      <c r="K574" s="0" t="s">
         <v>2345</v>
       </c>
-      <c r="E574" s="0" t="s">
+      <c r="L574" s="0" t="s">
         <v>2346</v>
-      </c>
-      <c r="F574" s="0" t="s">
-        <v>2347</v>
-      </c>
-      <c r="J574" s="0" t="s">
-        <v>2341</v>
-      </c>
-      <c r="K574" s="0" t="s">
-        <v>2342</v>
-      </c>
-      <c r="L574" s="0" t="s">
-        <v>2343</v>
       </c>
     </row>
     <row r="575" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A575" s="0" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="B575" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D575" s="0" t="s">
+        <v>2348</v>
+      </c>
+      <c r="E575" s="0" t="s">
         <v>2349</v>
       </c>
-      <c r="E575" s="0" t="s">
+      <c r="F575" s="0" t="s">
         <v>2350</v>
       </c>
-      <c r="F575" s="0" t="s">
-        <v>2351</v>
-      </c>
       <c r="J575" s="0" t="s">
-        <v>2352</v>
+        <v>2344</v>
       </c>
       <c r="K575" s="0" t="s">
-        <v>2353</v>
+        <v>2345</v>
       </c>
       <c r="L575" s="0" t="s">
-        <v>2354</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="576" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A576" s="0" t="s">
-        <v>2355</v>
+        <v>2351</v>
       </c>
       <c r="B576" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D576" s="0" t="s">
+        <v>2352</v>
+      </c>
+      <c r="E576" s="0" t="s">
+        <v>2353</v>
+      </c>
+      <c r="F576" s="0" t="s">
+        <v>2354</v>
+      </c>
+      <c r="J576" s="0" t="s">
+        <v>2355</v>
+      </c>
+      <c r="K576" s="0" t="s">
         <v>2356</v>
       </c>
-      <c r="E576" s="0" t="s">
+      <c r="L576" s="0" t="s">
         <v>2357</v>
-      </c>
-      <c r="F576" s="0" t="s">
-        <v>2358</v>
-      </c>
-      <c r="J576" s="0" t="s">
-        <v>2057</v>
-      </c>
-      <c r="K576" s="0" t="s">
-        <v>2058</v>
-      </c>
-      <c r="L576" s="0" t="s">
-        <v>2059</v>
       </c>
     </row>
     <row r="577" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A577" s="0" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="B577" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D577" s="0" t="s">
+        <v>2359</v>
+      </c>
+      <c r="E577" s="0" t="s">
         <v>2360</v>
       </c>
-      <c r="E577" s="0" t="s">
+      <c r="F577" s="0" t="s">
         <v>2361</v>
       </c>
-      <c r="F577" s="0" t="s">
-        <v>2362</v>
+      <c r="J577" s="0" t="s">
+        <v>2057</v>
+      </c>
+      <c r="K577" s="0" t="s">
+        <v>2058</v>
+      </c>
+      <c r="L577" s="0" t="s">
+        <v>2059</v>
       </c>
     </row>
     <row r="578" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A578" s="0" t="s">
+        <v>2362</v>
+      </c>
+      <c r="B578" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D578" s="0" t="s">
         <v>2363</v>
       </c>
-      <c r="B578" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="D578" s="0" t="s">
+      <c r="E578" s="0" t="s">
         <v>2364</v>
       </c>
-      <c r="E578" s="0" t="s">
+      <c r="F578" s="0" t="s">
         <v>2365</v>
-      </c>
-      <c r="F578" s="0" t="s">
-        <v>2366</v>
       </c>
     </row>
     <row r="579" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A579" s="0" t="s">
+        <v>2366</v>
+      </c>
+      <c r="B579" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D579" s="0" t="s">
         <v>2367</v>
       </c>
-      <c r="B579" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D579" s="0" t="s">
+      <c r="E579" s="0" t="s">
         <v>2368</v>
       </c>
-      <c r="E579" s="0" t="s">
+      <c r="F579" s="0" t="s">
         <v>2369</v>
-      </c>
-      <c r="F579" s="0" t="s">
-        <v>2370</v>
-      </c>
-      <c r="J579" s="0" t="s">
-        <v>2371</v>
-      </c>
-      <c r="K579" s="0" t="s">
-        <v>2372</v>
-      </c>
-      <c r="L579" s="0" t="s">
-        <v>2373</v>
       </c>
     </row>
     <row r="580" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A580" s="0" t="s">
+        <v>2370</v>
+      </c>
+      <c r="B580" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D580" s="0" t="s">
+        <v>2371</v>
+      </c>
+      <c r="E580" s="0" t="s">
+        <v>2372</v>
+      </c>
+      <c r="F580" s="0" t="s">
+        <v>2373</v>
+      </c>
+      <c r="J580" s="0" t="s">
         <v>2374</v>
       </c>
-      <c r="B580" s="0" t="s">
-        <v>284</v>
-      </c>
-      <c r="D580" s="0" t="s">
+      <c r="K580" s="0" t="s">
         <v>2375</v>
       </c>
-      <c r="E580" s="0" t="s">
-        <v>2374</v>
-      </c>
-      <c r="F580" s="0" t="s">
+      <c r="L580" s="0" t="s">
         <v>2376</v>
       </c>
     </row>
@@ -19747,115 +19756,115 @@
         <v>2377</v>
       </c>
       <c r="B581" s="0" t="s">
-        <v>13</v>
+        <v>284</v>
       </c>
       <c r="D581" s="0" t="s">
         <v>2378</v>
       </c>
       <c r="E581" s="0" t="s">
+        <v>2377</v>
+      </c>
+      <c r="F581" s="0" t="s">
         <v>2379</v>
-      </c>
-      <c r="F581" s="0" t="s">
-        <v>2380</v>
       </c>
     </row>
     <row r="582" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A582" s="0" t="s">
+        <v>2380</v>
+      </c>
+      <c r="B582" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D582" s="0" t="s">
         <v>2381</v>
       </c>
-      <c r="B582" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="D582" s="0" t="s">
+      <c r="E582" s="0" t="s">
         <v>2382</v>
       </c>
-      <c r="E582" s="0" t="s">
+      <c r="F582" s="0" t="s">
         <v>2383</v>
-      </c>
-      <c r="F582" s="0" t="s">
-        <v>2384</v>
       </c>
     </row>
     <row r="583" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A583" s="0" t="s">
+        <v>2384</v>
+      </c>
+      <c r="B583" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D583" s="0" t="s">
         <v>2385</v>
       </c>
-      <c r="B583" s="0" t="s">
-        <v>166</v>
-      </c>
-      <c r="D583" s="0" t="s">
+      <c r="E583" s="0" t="s">
         <v>2386</v>
       </c>
-      <c r="E583" s="0" t="s">
+      <c r="F583" s="0" t="s">
         <v>2387</v>
-      </c>
-      <c r="F583" s="0" t="s">
-        <v>2388</v>
       </c>
     </row>
     <row r="584" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A584" s="0" t="s">
+        <v>2388</v>
+      </c>
+      <c r="B584" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="D584" s="0" t="s">
         <v>2389</v>
       </c>
-      <c r="B584" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="D584" s="0" t="s">
+      <c r="E584" s="0" t="s">
         <v>2390</v>
       </c>
-      <c r="E584" s="0" t="s">
+      <c r="F584" s="0" t="s">
         <v>2391</v>
-      </c>
-      <c r="F584" s="0" t="s">
-        <v>2392</v>
       </c>
     </row>
     <row r="585" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A585" s="0" t="s">
+        <v>2392</v>
+      </c>
+      <c r="B585" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="D585" s="0" t="s">
         <v>2393</v>
       </c>
-      <c r="B585" s="0" t="s">
-        <v>312</v>
-      </c>
-      <c r="D585" s="0" t="s">
+      <c r="E585" s="0" t="s">
         <v>2394</v>
       </c>
-      <c r="E585" s="0" t="s">
+      <c r="F585" s="0" t="s">
         <v>2395</v>
-      </c>
-      <c r="F585" s="0" t="s">
-        <v>2396</v>
       </c>
     </row>
     <row r="586" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A586" s="0" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="B586" s="0" t="s">
         <v>312</v>
       </c>
       <c r="D586" s="0" t="s">
+        <v>2397</v>
+      </c>
+      <c r="E586" s="0" t="s">
         <v>2398</v>
       </c>
-      <c r="E586" s="0" t="s">
+      <c r="F586" s="0" t="s">
         <v>2399</v>
-      </c>
-      <c r="F586" s="0" t="s">
-        <v>2400</v>
       </c>
     </row>
     <row r="587" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A587" s="0" t="s">
+        <v>2400</v>
+      </c>
+      <c r="B587" s="0" t="s">
+        <v>312</v>
+      </c>
+      <c r="D587" s="0" t="s">
         <v>2401</v>
       </c>
-      <c r="B587" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D587" s="0" t="s">
+      <c r="E587" s="0" t="s">
         <v>2402</v>
-      </c>
-      <c r="E587" s="0" t="s">
-        <v>2401</v>
       </c>
       <c r="F587" s="0" t="s">
         <v>2403</v>
@@ -19872,417 +19881,434 @@
         <v>2405</v>
       </c>
       <c r="E588" s="0" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F588" s="0" t="s">
         <v>2406</v>
-      </c>
-      <c r="F588" s="0" t="s">
-        <v>2407</v>
       </c>
     </row>
     <row r="589" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A589" s="0" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="B589" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D589" s="0" t="s">
+        <v>2408</v>
+      </c>
+      <c r="E589" s="0" t="s">
         <v>2409</v>
       </c>
-      <c r="E589" s="0" t="s">
+      <c r="F589" s="0" t="s">
         <v>2410</v>
-      </c>
-      <c r="F589" s="0" t="s">
-        <v>2411</v>
-      </c>
-      <c r="J589" s="0" t="s">
-        <v>2412</v>
-      </c>
-      <c r="K589" s="0" t="s">
-        <v>2413</v>
-      </c>
-      <c r="L589" s="0" t="s">
-        <v>2414</v>
       </c>
     </row>
     <row r="590" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A590" s="0" t="s">
+        <v>2411</v>
+      </c>
+      <c r="B590" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D590" s="0" t="s">
+        <v>2412</v>
+      </c>
+      <c r="E590" s="0" t="s">
+        <v>2413</v>
+      </c>
+      <c r="F590" s="0" t="s">
+        <v>2414</v>
+      </c>
+      <c r="J590" s="0" t="s">
         <v>2415</v>
       </c>
-      <c r="B590" s="0" t="s">
-        <v>1320</v>
-      </c>
-      <c r="D590" s="0" t="s">
+      <c r="K590" s="0" t="s">
         <v>2416</v>
       </c>
-      <c r="E590" s="0" t="s">
+      <c r="L590" s="0" t="s">
         <v>2417</v>
-      </c>
-      <c r="F590" s="0" t="s">
-        <v>2418</v>
       </c>
     </row>
     <row r="591" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A591" s="0" t="s">
+        <v>2418</v>
+      </c>
+      <c r="B591" s="0" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D591" s="0" t="s">
         <v>2419</v>
       </c>
-      <c r="B591" s="0" t="s">
-        <v>1291</v>
-      </c>
-      <c r="D591" s="0" t="s">
+      <c r="E591" s="0" t="s">
         <v>2420</v>
       </c>
-      <c r="E591" s="0" t="s">
+      <c r="F591" s="0" t="s">
         <v>2421</v>
-      </c>
-      <c r="F591" s="0" t="s">
-        <v>2422</v>
-      </c>
-      <c r="J591" s="0" t="s">
-        <v>2423</v>
-      </c>
-      <c r="K591" s="0" t="s">
-        <v>2424</v>
-      </c>
-      <c r="L591" s="0" t="s">
-        <v>2425</v>
       </c>
     </row>
     <row r="592" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A592" s="0" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B592" s="0" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D592" s="0" t="s">
+        <v>2423</v>
+      </c>
+      <c r="E592" s="0" t="s">
+        <v>2424</v>
+      </c>
+      <c r="F592" s="0" t="s">
+        <v>2425</v>
+      </c>
+      <c r="J592" s="0" t="s">
         <v>2426</v>
       </c>
-      <c r="B592" s="0" t="s">
-        <v>474</v>
-      </c>
-      <c r="D592" s="0" t="s">
+      <c r="K592" s="0" t="s">
         <v>2427</v>
       </c>
-      <c r="E592" s="0" t="s">
+      <c r="L592" s="0" t="s">
         <v>2428</v>
-      </c>
-      <c r="F592" s="0" t="s">
-        <v>2429</v>
-      </c>
-      <c r="J592" s="0" t="s">
-        <v>2430</v>
-      </c>
-      <c r="K592" s="0" t="s">
-        <v>2431</v>
-      </c>
-      <c r="L592" s="0" t="s">
-        <v>2432</v>
       </c>
     </row>
     <row r="593" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A593" s="0" t="s">
+        <v>2429</v>
+      </c>
+      <c r="B593" s="0" t="s">
+        <v>474</v>
+      </c>
+      <c r="D593" s="0" t="s">
+        <v>2430</v>
+      </c>
+      <c r="E593" s="0" t="s">
+        <v>2431</v>
+      </c>
+      <c r="F593" s="0" t="s">
+        <v>2432</v>
+      </c>
+      <c r="J593" s="0" t="s">
         <v>2433</v>
       </c>
-      <c r="B593" s="0" t="s">
-        <v>565</v>
-      </c>
-      <c r="D593" s="0" t="s">
+      <c r="K593" s="0" t="s">
         <v>2434</v>
       </c>
-      <c r="E593" s="0" t="s">
+      <c r="L593" s="0" t="s">
         <v>2435</v>
-      </c>
-      <c r="F593" s="0" t="s">
-        <v>2436</v>
-      </c>
-      <c r="J593" s="0" t="s">
-        <v>2437</v>
-      </c>
-      <c r="K593" s="0" t="s">
-        <v>2438</v>
-      </c>
-      <c r="L593" s="0" t="s">
-        <v>2439</v>
       </c>
     </row>
     <row r="594" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A594" s="0" t="s">
+        <v>2436</v>
+      </c>
+      <c r="B594" s="0" t="s">
+        <v>565</v>
+      </c>
+      <c r="D594" s="0" t="s">
+        <v>2437</v>
+      </c>
+      <c r="E594" s="0" t="s">
+        <v>2438</v>
+      </c>
+      <c r="F594" s="0" t="s">
+        <v>2439</v>
+      </c>
+      <c r="J594" s="0" t="s">
         <v>2440</v>
       </c>
-      <c r="B594" s="0" t="s">
-        <v>240</v>
-      </c>
-      <c r="D594" s="0" t="s">
+      <c r="K594" s="0" t="s">
         <v>2441</v>
       </c>
-      <c r="E594" s="0" t="s">
+      <c r="L594" s="0" t="s">
         <v>2442</v>
-      </c>
-      <c r="F594" s="0" t="s">
-        <v>2443</v>
-      </c>
-      <c r="J594" s="0" t="s">
-        <v>2437</v>
-      </c>
-      <c r="K594" s="0" t="s">
-        <v>2438</v>
-      </c>
-      <c r="L594" s="0" t="s">
-        <v>2439</v>
       </c>
     </row>
     <row r="595" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A595" s="0" t="s">
+        <v>2443</v>
+      </c>
+      <c r="B595" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="D595" s="0" t="s">
         <v>2444</v>
       </c>
-      <c r="B595" s="0" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D595" s="0" t="s">
+      <c r="E595" s="0" t="s">
         <v>2445</v>
       </c>
-      <c r="E595" s="0" t="s">
+      <c r="F595" s="0" t="s">
         <v>2446</v>
       </c>
-      <c r="F595" s="0" t="s">
-        <v>2447</v>
-      </c>
       <c r="J595" s="0" t="s">
-        <v>2448</v>
+        <v>2440</v>
       </c>
       <c r="K595" s="0" t="s">
-        <v>2449</v>
+        <v>2441</v>
       </c>
       <c r="L595" s="0" t="s">
-        <v>2450</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="596" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A596" s="0" t="s">
-        <v>2451</v>
+        <v>2447</v>
       </c>
       <c r="B596" s="0" t="s">
         <v>1022</v>
       </c>
       <c r="D596" s="0" t="s">
+        <v>2448</v>
+      </c>
+      <c r="E596" s="0" t="s">
+        <v>2449</v>
+      </c>
+      <c r="F596" s="0" t="s">
+        <v>2450</v>
+      </c>
+      <c r="J596" s="0" t="s">
+        <v>2451</v>
+      </c>
+      <c r="K596" s="0" t="s">
         <v>2452</v>
       </c>
-      <c r="E596" s="0" t="s">
+      <c r="L596" s="0" t="s">
         <v>2453</v>
-      </c>
-      <c r="F596" s="0" t="s">
-        <v>2454</v>
-      </c>
-      <c r="J596" s="0" t="s">
-        <v>2455</v>
-      </c>
-      <c r="K596" s="0" t="s">
-        <v>2456</v>
-      </c>
-      <c r="L596" s="0" t="s">
-        <v>2457</v>
       </c>
     </row>
     <row r="597" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A597" s="0" t="s">
+        <v>2454</v>
+      </c>
+      <c r="B597" s="0" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D597" s="0" t="s">
+        <v>2455</v>
+      </c>
+      <c r="E597" s="0" t="s">
+        <v>2456</v>
+      </c>
+      <c r="F597" s="0" t="s">
+        <v>2457</v>
+      </c>
+      <c r="J597" s="0" t="s">
         <v>2458</v>
       </c>
-      <c r="B597" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D597" s="0" t="s">
+      <c r="K597" s="0" t="s">
         <v>2459</v>
       </c>
-      <c r="E597" s="0" t="s">
+      <c r="L597" s="0" t="s">
         <v>2460</v>
-      </c>
-      <c r="F597" s="0" t="s">
-        <v>2461</v>
-      </c>
-      <c r="J597" s="0" t="s">
-        <v>2462</v>
-      </c>
-      <c r="K597" s="0" t="s">
-        <v>2463</v>
-      </c>
-      <c r="L597" s="0" t="s">
-        <v>2464</v>
       </c>
     </row>
     <row r="598" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A598" s="0" t="s">
-        <v>2465</v>
+        <v>2461</v>
       </c>
       <c r="B598" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D598" s="0" t="s">
+        <v>2462</v>
+      </c>
+      <c r="E598" s="0" t="s">
+        <v>2463</v>
+      </c>
+      <c r="F598" s="0" t="s">
+        <v>2464</v>
+      </c>
+      <c r="J598" s="0" t="s">
+        <v>2465</v>
+      </c>
+      <c r="K598" s="0" t="s">
         <v>2466</v>
       </c>
-      <c r="E598" s="0" t="s">
+      <c r="L598" s="0" t="s">
         <v>2467</v>
-      </c>
-      <c r="F598" s="0" t="s">
-        <v>2468</v>
-      </c>
-      <c r="J598" s="0" t="s">
-        <v>2469</v>
-      </c>
-      <c r="K598" s="0" t="s">
-        <v>2470</v>
-      </c>
-      <c r="L598" s="0" t="s">
-        <v>2471</v>
       </c>
     </row>
     <row r="599" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A599" s="0" t="s">
-        <v>2472</v>
+        <v>2468</v>
       </c>
       <c r="B599" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D599" s="0" t="s">
+        <v>2469</v>
+      </c>
+      <c r="E599" s="0" t="s">
+        <v>2470</v>
+      </c>
+      <c r="F599" s="0" t="s">
+        <v>2471</v>
+      </c>
+      <c r="J599" s="0" t="s">
+        <v>2472</v>
+      </c>
+      <c r="K599" s="0" t="s">
         <v>2473</v>
       </c>
-      <c r="E599" s="0" t="s">
+      <c r="L599" s="0" t="s">
         <v>2474</v>
-      </c>
-      <c r="F599" s="0" t="s">
-        <v>2475</v>
-      </c>
-      <c r="J599" s="0" t="s">
-        <v>2476</v>
-      </c>
-      <c r="K599" s="0" t="s">
-        <v>2477</v>
-      </c>
-      <c r="L599" s="0" t="s">
-        <v>2478</v>
       </c>
     </row>
     <row r="600" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A600" s="0" t="s">
+        <v>2475</v>
+      </c>
+      <c r="B600" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D600" s="0" t="s">
+        <v>2476</v>
+      </c>
+      <c r="E600" s="0" t="s">
+        <v>2477</v>
+      </c>
+      <c r="F600" s="0" t="s">
+        <v>2478</v>
+      </c>
+      <c r="J600" s="0" t="s">
         <v>2479</v>
       </c>
-      <c r="B600" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="D600" s="0" t="s">
+      <c r="K600" s="0" t="s">
         <v>2480</v>
       </c>
-      <c r="E600" s="0" t="s">
+      <c r="L600" s="0" t="s">
         <v>2481</v>
-      </c>
-      <c r="F600" s="0" t="s">
-        <v>2482</v>
-      </c>
-      <c r="J600" s="0" t="s">
-        <v>2483</v>
-      </c>
-      <c r="K600" s="0" t="s">
-        <v>2484</v>
-      </c>
-      <c r="L600" s="0" t="s">
-        <v>2485</v>
       </c>
     </row>
     <row r="601" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A601" s="0" t="s">
+        <v>2482</v>
+      </c>
+      <c r="B601" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D601" s="0" t="s">
+        <v>2483</v>
+      </c>
+      <c r="E601" s="0" t="s">
+        <v>2484</v>
+      </c>
+      <c r="F601" s="0" t="s">
+        <v>2485</v>
+      </c>
+      <c r="J601" s="0" t="s">
         <v>2486</v>
       </c>
-      <c r="B601" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D601" s="0" t="s">
+      <c r="K601" s="0" t="s">
         <v>2487</v>
       </c>
-      <c r="E601" s="0" t="s">
+      <c r="L601" s="0" t="s">
         <v>2488</v>
-      </c>
-      <c r="F601" s="0" t="s">
-        <v>2489</v>
-      </c>
-      <c r="J601" s="0" t="s">
-        <v>2490</v>
-      </c>
-      <c r="K601" s="0" t="s">
-        <v>2491</v>
-      </c>
-      <c r="L601" s="0" t="s">
-        <v>2492</v>
       </c>
     </row>
     <row r="602" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A602" s="0" t="s">
-        <v>2493</v>
+        <v>2489</v>
       </c>
       <c r="B602" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D602" s="0" t="s">
+        <v>2490</v>
+      </c>
+      <c r="E602" s="0" t="s">
+        <v>2491</v>
+      </c>
+      <c r="F602" s="0" t="s">
+        <v>2492</v>
+      </c>
+      <c r="J602" s="0" t="s">
+        <v>2493</v>
+      </c>
+      <c r="K602" s="0" t="s">
         <v>2494</v>
       </c>
-      <c r="E602" s="0" t="s">
+      <c r="L602" s="0" t="s">
         <v>2495</v>
-      </c>
-      <c r="F602" s="0" t="s">
-        <v>2496</v>
-      </c>
-      <c r="J602" s="0" t="s">
-        <v>2497</v>
-      </c>
-      <c r="K602" s="0" t="s">
-        <v>2498</v>
-      </c>
-      <c r="L602" s="0" t="s">
-        <v>2499</v>
       </c>
     </row>
     <row r="603" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A603" s="0" t="s">
-        <v>2500</v>
+        <v>2496</v>
       </c>
       <c r="B603" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D603" s="0" t="s">
-        <v>1493</v>
+        <v>2497</v>
       </c>
       <c r="E603" s="0" t="s">
-        <v>1494</v>
+        <v>2498</v>
       </c>
       <c r="F603" s="0" t="s">
-        <v>1495</v>
+        <v>2499</v>
       </c>
       <c r="J603" s="0" t="s">
-        <v>1496</v>
+        <v>2500</v>
       </c>
       <c r="K603" s="0" t="s">
-        <v>1497</v>
+        <v>2501</v>
       </c>
       <c r="L603" s="0" t="s">
-        <v>1498</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="604" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A604" s="0" t="s">
-        <v>2501</v>
+        <v>2503</v>
       </c>
       <c r="B604" s="0" t="s">
-        <v>2502</v>
+        <v>13</v>
       </c>
       <c r="D604" s="0" t="s">
-        <v>2503</v>
+        <v>1493</v>
       </c>
       <c r="E604" s="0" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F604" s="0" t="s">
+        <v>1495</v>
+      </c>
+      <c r="J604" s="0" t="s">
+        <v>1496</v>
+      </c>
+      <c r="K604" s="0" t="s">
+        <v>1497</v>
+      </c>
+      <c r="L604" s="0" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="605" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A605" s="0" t="s">
         <v>2504</v>
       </c>
-      <c r="F604" s="0" t="s">
+      <c r="B605" s="0" t="s">
         <v>2505</v>
       </c>
-      <c r="J604" s="0" t="s">
+      <c r="D605" s="0" t="s">
         <v>2506</v>
       </c>
-      <c r="K604" s="0" t="s">
+      <c r="E605" s="0" t="s">
         <v>2507</v>
       </c>
-      <c r="L604" s="0" t="s">
+      <c r="F605" s="0" t="s">
         <v>2508</v>
+      </c>
+      <c r="J605" s="0" t="s">
+        <v>2509</v>
+      </c>
+      <c r="K605" s="0" t="s">
+        <v>2510</v>
+      </c>
+      <c r="L605" s="0" t="s">
+        <v>2511</v>
       </c>
     </row>
   </sheetData>
